--- a/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,54</t>
+          <t>0,0; 48,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,57</t>
+          <t>0,0; 23,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 25,78</t>
+          <t>2,74; 26,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,48</t>
+          <t>-1,79; 1,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,77</t>
+          <t>-2,15; 0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 31,47</t>
+          <t>-1,21; 24,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,01</t>
+          <t>-0,84; 2,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,18</t>
+          <t>-1,77; 0,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,5</t>
+          <t>-0,88; 1,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,1</t>
+          <t>-1,51; 0,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 10,16</t>
+          <t>-0,75; 8,7</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 895,37</t>
+          <t>-84,01; 579,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,95</t>
+          <t>-1,05; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,27</t>
+          <t>-1,38; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,05</t>
+          <t>-0,9; 5,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,03</t>
+          <t>-1,91; 1,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,74</t>
+          <t>-1,52; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,9</t>
+          <t>-2,0; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,09</t>
+          <t>-1,0; 1,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,1</t>
+          <t>-1,09; 1,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,67</t>
+          <t>-1,09; 2,52</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 702,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,37; 157,55</t>
+          <t>-78,99; 137,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 233,05</t>
+          <t>-64,78; 191,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,5</t>
+          <t>-100,0; 235,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,14; 166,28</t>
+          <t>-56,16; 148,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 153,86</t>
+          <t>-59,55; 151,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 331,37</t>
+          <t>-74,77; 285,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,72</t>
+          <t>-0,42; 1,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,02</t>
+          <t>0,35; 3,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 17,75</t>
+          <t>4,49; 17,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,96</t>
+          <t>-2,21; 2,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,96</t>
+          <t>-2,32; 1,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 11,43</t>
+          <t>2,54; 11,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,44</t>
+          <t>-0,88; 1,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,27</t>
+          <t>-0,33; 2,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,6</t>
+          <t>4,56; 12,07</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,27; —</t>
+          <t>1,07; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 755,75</t>
+          <t>-82,96; 810,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 1008,88</t>
+          <t>-60,0; 946,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>226,61; 6082,43</t>
+          <t>178,4; 5556,08</t>
         </is>
       </c>
     </row>
@@ -1546,42 +1546,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,84; 29,25</t>
+          <t>10,81; 28,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,48</t>
+          <t>-0,05; 5,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,95</t>
+          <t>-1,85; 0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 15,99</t>
+          <t>4,72; 16,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,45</t>
+          <t>0,05; 3,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,84</t>
+          <t>-0,8; 1,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,08; 19,49</t>
+          <t>8,73; 19,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,27</t>
+          <t>-1,46; 1,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,6</t>
+          <t>-2,15; 0,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12,45; 32,32</t>
+          <t>13,29; 32,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,56</t>
+          <t>-0,94; 0,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,41</t>
+          <t>-0,29; 2,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 26,01</t>
+          <t>0,65; 26,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,62</t>
+          <t>-0,85; 0,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,26</t>
+          <t>-0,53; 1,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,95; 24,75</t>
+          <t>1,25; 25,2</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>559,32; —</t>
+          <t>616,75; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,9; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71,39; 6157,37</t>
+          <t>100,36; 7719,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,23</t>
+          <t>-0,79; 1,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,3</t>
+          <t>-0,87; 1,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38,43; 54,95</t>
+          <t>38,34; 54,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,61</t>
+          <t>-0,06; 2,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,99</t>
+          <t>-0,35; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,85; 51,76</t>
+          <t>41,18; 51,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,78</t>
+          <t>-0,19; 1,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,5</t>
+          <t>-0,31; 1,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>42,33; 51,27</t>
+          <t>41,87; 51,12</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3918,82; —</t>
+          <t>3787,42; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,73</t>
+          <t>-0,3; 0,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,95</t>
+          <t>-0,21; 0,9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,43</t>
+          <t>13,05; 19,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,95</t>
+          <t>-0,29; 0,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,84</t>
+          <t>-0,34; 0,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,65; 17,39</t>
+          <t>6,51; 17,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,16; 0,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,18; 0,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,05</t>
+          <t>7,8; 17,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 206,99</t>
+          <t>-41,25; 237,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 292,54</t>
+          <t>-31,9; 262,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1334,07; 5507,74</t>
+          <t>1426,03; 5527,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 198,03</t>
+          <t>-29,81; 190,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 172,11</t>
+          <t>-34,69; 166,19</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>634,53; 2977,19</t>
+          <t>660,06; 2867,39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 139,92</t>
+          <t>-18,2; 136,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 133,0</t>
+          <t>-20,02; 137,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1052,54; 3156,47</t>
+          <t>1063,87; 3273,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>7,68</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,86</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 14,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 26,83</t>
+          <t>1,85; 19,95</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,25</t>
+          <t>-1,72; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,84</t>
+          <t>-2,29; 0,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 24,34</t>
+          <t>-1,22; 27,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,09</t>
+          <t>-0,76; 2,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,17</t>
+          <t>-0,78; 5,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,21</t>
+          <t>-0,92; 1,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,05</t>
+          <t>-1,46; 0,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 8,7</t>
+          <t>-0,64; 9,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>614,76%</t>
+          <t>563,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-68,57%</t>
+          <t>139,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>240,3%</t>
+          <t>336,37%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 579,28</t>
+          <t>-87,28; 559,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,02</t>
+          <t>-1,04; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,49</t>
+          <t>-1,25; 1,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,5</t>
+          <t>-1,06; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,08</t>
+          <t>-1,64; 1,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,6</t>
+          <t>-1,56; 1,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,9</t>
+          <t>-2,04; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,14</t>
+          <t>-1,07; 1,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,23</t>
+          <t>-0,9; 1,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,52</t>
+          <t>-1,13; 1,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116,44%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-29,76%</t>
+          <t>-37,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>-5,5%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,34; 607,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,99; 137,79</t>
+          <t>-73,57; 186,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 191,28</t>
+          <t>-67,07; 185,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 235,97</t>
+          <t>-100,0; 268,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 148,78</t>
+          <t>-59,94; 149,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 151,65</t>
+          <t>-57,25; 164,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 285,51</t>
+          <t>-76,34; 248,35</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>7,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,67</t>
+          <t>-0,42; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,95</t>
+          <t>0,35; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 17,69</t>
+          <t>3,89; 15,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,04</t>
+          <t>-2,6; 2,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,93</t>
+          <t>-2,38; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,47</t>
+          <t>2,91; 10,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,49</t>
+          <t>-0,85; 1,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,38</t>
+          <t>-0,25; 2,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 12,07</t>
+          <t>4,74; 11,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3124,09%</t>
+          <t>2829,32%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>564,4%</t>
+          <t>561,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1174,21%</t>
+          <t>1107,88%</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07; —</t>
+          <t>17,8; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 810,16</t>
+          <t>-73,05; 809,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 946,63</t>
+          <t>-46,3; 1128,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>178,4; 5556,08</t>
+          <t>251,1; 7570,98</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,38</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>12,88</t>
         </is>
       </c>
     </row>
@@ -1546,42 +1546,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 28,72</t>
+          <t>9,97; 28,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,29</t>
+          <t>0,32; 5,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,95</t>
+          <t>-1,86; 0,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,72</t>
+          <t>4,67; 15,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,17</t>
+          <t>-0,11; 3,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,88</t>
+          <t>-0,84; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 19,67</t>
+          <t>8,33; 19,03</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1571,33%</t>
+          <t>1489,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3451,45%</t>
+          <t>3234,73%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>21,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>23,64</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>22,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,05</t>
+          <t>-1,47; 1,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,58</t>
+          <t>-1,96; 0,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,29; 32,66</t>
+          <t>12,75; 32,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,57</t>
+          <t>-0,93; 0,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,4</t>
+          <t>-0,29; 2,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,65; 26,2</t>
+          <t>16,61; 31,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,63</t>
+          <t>-1,0; 0,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,25</t>
+          <t>-0,57; 1,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 25,2</t>
+          <t>17,08; 28,87</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2983,9%</t>
+          <t>3043,76%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1757,11%</t>
+          <t>7680,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1500,3%</t>
+          <t>4612,83%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>616,75; —</t>
+          <t>707,17; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100,36; 7719,71</t>
+          <t>1593,95; 18707,45</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47,21</t>
+          <t>45,57</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,46</t>
+          <t>45,99</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>46,69</t>
+          <t>45,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,6</t>
+          <t>-0,79; 1,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,49</t>
+          <t>-0,88; 1,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38,34; 54,93</t>
+          <t>37,52; 53,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,82</t>
+          <t>-0,37; 2,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,32</t>
+          <t>-0,36; 2,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,18; 51,61</t>
+          <t>40,2; 50,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,72</t>
+          <t>-0,18; 1,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,51</t>
+          <t>-0,33; 1,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>41,87; 51,12</t>
+          <t>41,35; 50,25</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12063,71%</t>
+          <t>11642,99%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13762,88%</t>
+          <t>13626,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13030,21%</t>
+          <t>12797,84%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,9; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3787,42; —</t>
+          <t>3560,69; —</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>15,89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>15,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,79</t>
+          <t>-0,38; 0,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,9</t>
+          <t>-0,25; 0,91</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,76</t>
+          <t>11,95; 18,25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,96</t>
+          <t>-0,2; 1,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,8</t>
+          <t>-0,38; 0,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,51; 17,38</t>
+          <t>13,85; 17,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,68</t>
+          <t>-0,09; 0,71</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,66</t>
+          <t>-0,12; 0,67</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,8; 17,09</t>
+          <t>13,68; 17,29</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2772,29%</t>
+          <t>2513,39%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1641,36%</t>
+          <t>2063,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2028,51%</t>
+          <t>2244,72%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 237,38</t>
+          <t>-45,78; 232,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 262,82</t>
+          <t>-38,34; 311,74</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1426,03; 5527,47</t>
+          <t>1172,66; 5418,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 190,34</t>
+          <t>-25,37; 211,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 166,19</t>
+          <t>-35,7; 150,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>660,06; 2867,39</t>
+          <t>1197,08; 3695,86</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 136,33</t>
+          <t>-10,37; 148,54</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 137,04</t>
+          <t>-14,8; 143,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1063,87; 3273,38</t>
+          <t>1480,24; 3585,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
